--- a/web/src/main/resources/salon-log-template.xlsx
+++ b/web/src/main/resources/salon-log-template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Salon — rapport fin de journée</t>
   </si>
@@ -21,7 +21,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>(le nom du fichier fait foi : TT-jj-MM-aaaa.xlsx)</t>
+    <t>(le nom du fichier fait foi : SA-jj-MM-aaaa.xlsx)</t>
   </si>
   <si>
     <t>Total ventes</t>
@@ -39,50 +39,61 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Les cases jaunes se remplissent ; le reste se calcule. Ajoutez des lignes au tableau si besoin (jusqu'à la ligne 60).</t>
-  </si>
-  <si>
-    <t>Rubrique</t>
-  </si>
-  <si>
-    <t>Désignation</t>
+    <t>Remises du jour</t>
+  </si>
+  <si>
+    <t>Une ligne par client : les cases jaunes se remplissent, le reste se calcule. Le total se fait tout seul.</t>
+  </si>
+  <si>
+    <t>Heure</t>
+  </si>
+  <si>
+    <t>Prestation</t>
+  </si>
+  <si>
+    <t>Employé(e)</t>
   </si>
   <si>
     <t>Prix</t>
   </si>
   <si>
-    <t>Quantité</t>
+    <t>Remise</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Coiffure</t>
+    <t>09:30</t>
   </si>
   <si>
     <t>Coupe</t>
   </si>
   <si>
+    <t>Samira</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
     <t>Brushing</t>
   </si>
   <si>
+    <t>11:00</t>
+  </si>
+  <si>
     <t>Coloration</t>
   </si>
   <si>
-    <t>Soins</t>
-  </si>
-  <si>
-    <t>Soin visage</t>
-  </si>
-  <si>
-    <t>Manucure</t>
+    <t>Nadia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="HH:mm"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11.0"/>
@@ -132,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -140,20 +151,22 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.0" customWidth="true"/>
-    <col min="2" max="2" width="30.0" customWidth="true"/>
-    <col min="3" max="3" width="12.0" customWidth="true"/>
-    <col min="4" max="4" width="12.0" customWidth="true"/>
-    <col min="5" max="5" width="14.0" customWidth="true"/>
+    <col min="1" max="1" width="9.0" customWidth="true"/>
+    <col min="2" max="2" width="28.0" customWidth="true"/>
+    <col min="3" max="3" width="16.0" customWidth="true"/>
+    <col min="4" max="4" width="11.0" customWidth="true"/>
+    <col min="5" max="5" width="11.0" customWidth="true"/>
+    <col min="6" max="6" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -174,7 +187,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <f>SUM(E13:E60)</f>
+        <f>SUM(F13:F80)</f>
       </c>
     </row>
     <row r="6">
@@ -197,410 +210,751 @@
       <c r="A8" t="s" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="0">
+        <f>COUNTA(B13:B80)</f>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="6"/>
+      <c r="D9" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM(E13:E80)</f>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s" s="1">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F12" t="s" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C13" t="n" s="5">
+      <c r="A13" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s" s="6">
+        <v>18</v>
+      </c>
+      <c r="D13" t="n" s="5">
         <v>80.0</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="3">
-        <f>C13*D13</f>
+      <c r="E13" s="5"/>
+      <c r="F13" s="3">
+        <f>D13-E13</f>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n" s="5">
+      <c r="A14" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s" s="6">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s" s="6">
+        <v>18</v>
+      </c>
+      <c r="D14" t="n" s="5">
         <v>100.0</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="3">
-        <f>C14*D14</f>
+      <c r="E14" t="n" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F14" s="3">
+        <f>D14-E14</f>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C15" t="n" s="5">
+      <c r="A15" t="s" s="7">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s" s="6">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s" s="6">
+        <v>23</v>
+      </c>
+      <c r="D15" t="n" s="5">
         <v>250.0</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="3">
-        <f>C15*D15</f>
+      <c r="E15" s="5"/>
+      <c r="F15" s="3">
+        <f>D15-E15</f>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C16" t="n" s="5">
-        <v>200.0</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="3">
-        <f>C16*D16</f>
+      <c r="A16" s="7"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="3">
+        <f>IF(D16="","",D16-E16)</f>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C17" t="n" s="5">
-        <v>80.0</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="3">
-        <f>C17*D17</f>
+      <c r="A17" s="7"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="3">
+        <f>IF(D17="","",D17-E17)</f>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="3">
-        <f>C18*D18</f>
+      <c r="A18" s="7"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="3">
+        <f>IF(D18="","",D18-E18)</f>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="3">
-        <f>C19*D19</f>
+      <c r="A19" s="7"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="3">
+        <f>IF(D19="","",D19-E19)</f>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="3">
-        <f>C20*D20</f>
+      <c r="A20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="3">
+        <f>IF(D20="","",D20-E20)</f>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="3">
-        <f>C21*D21</f>
+      <c r="A21" s="7"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="3">
+        <f>IF(D21="","",D21-E21)</f>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="3">
-        <f>C22*D22</f>
+      <c r="A22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="3">
+        <f>IF(D22="","",D22-E22)</f>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="3">
-        <f>C23*D23</f>
+      <c r="A23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="3">
+        <f>IF(D23="","",D23-E23)</f>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="5"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="3">
-        <f>C24*D24</f>
+      <c r="A24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="3">
+        <f>IF(D24="","",D24-E24)</f>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="5"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="3">
-        <f>C25*D25</f>
+      <c r="A25" s="7"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="3">
+        <f>IF(D25="","",D25-E25)</f>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="3">
-        <f>C26*D26</f>
+      <c r="A26" s="7"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="3">
+        <f>IF(D26="","",D26-E26)</f>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="5"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="3">
-        <f>C27*D27</f>
+      <c r="A27" s="7"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="3">
+        <f>IF(D27="","",D27-E27)</f>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="5"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="3">
-        <f>C28*D28</f>
+      <c r="A28" s="7"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="3">
+        <f>IF(D28="","",D28-E28)</f>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="5"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="3">
-        <f>C29*D29</f>
+      <c r="A29" s="7"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="3">
+        <f>IF(D29="","",D29-E29)</f>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="5"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="3">
-        <f>C30*D30</f>
+      <c r="A30" s="7"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="3">
+        <f>IF(D30="","",D30-E30)</f>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="5"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="3">
-        <f>C31*D31</f>
+      <c r="A31" s="7"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="3">
+        <f>IF(D31="","",D31-E31)</f>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="5"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="3">
-        <f>C32*D32</f>
+      <c r="A32" s="7"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="3">
+        <f>IF(D32="","",D32-E32)</f>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="5"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="3">
-        <f>C33*D33</f>
+      <c r="A33" s="7"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="3">
+        <f>IF(D33="","",D33-E33)</f>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="5"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="3">
-        <f>C34*D34</f>
+      <c r="A34" s="7"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="3">
+        <f>IF(D34="","",D34-E34)</f>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="5"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="3">
-        <f>C35*D35</f>
+      <c r="A35" s="7"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="3">
+        <f>IF(D35="","",D35-E35)</f>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="5"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="3">
-        <f>C36*D36</f>
+      <c r="A36" s="7"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="3">
+        <f>IF(D36="","",D36-E36)</f>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="5"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="3">
-        <f>C37*D37</f>
+      <c r="A37" s="7"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="3">
+        <f>IF(D37="","",D37-E37)</f>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="5"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="3">
-        <f>C38*D38</f>
+      <c r="A38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="3">
+        <f>IF(D38="","",D38-E38)</f>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="5"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="3">
-        <f>C39*D39</f>
+      <c r="A39" s="7"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="3">
+        <f>IF(D39="","",D39-E39)</f>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="5"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="3">
-        <f>C40*D40</f>
+      <c r="A40" s="7"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="3">
+        <f>IF(D40="","",D40-E40)</f>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="5"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="3">
-        <f>C41*D41</f>
+      <c r="A41" s="7"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="3">
+        <f>IF(D41="","",D41-E41)</f>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="5"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="3">
-        <f>C42*D42</f>
+      <c r="A42" s="7"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="3">
+        <f>IF(D42="","",D42-E42)</f>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="5"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="3">
-        <f>C43*D43</f>
+      <c r="A43" s="7"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="3">
+        <f>IF(D43="","",D43-E43)</f>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="5"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="3">
-        <f>C44*D44</f>
+      <c r="A44" s="7"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="3">
+        <f>IF(D44="","",D44-E44)</f>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="5"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="3">
-        <f>C45*D45</f>
+      <c r="A45" s="7"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="3">
+        <f>IF(D45="","",D45-E45)</f>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="5"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="3">
-        <f>C46*D46</f>
+      <c r="A46" s="7"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="3">
+        <f>IF(D46="","",D46-E46)</f>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="5"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="3">
-        <f>C47*D47</f>
+      <c r="A47" s="7"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="3">
+        <f>IF(D47="","",D47-E47)</f>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="5"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="3">
-        <f>C48*D48</f>
+      <c r="A48" s="7"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="3">
+        <f>IF(D48="","",D48-E48)</f>
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="5"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="3">
-        <f>C49*D49</f>
+      <c r="A49" s="7"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="3">
+        <f>IF(D49="","",D49-E49)</f>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="5"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="3">
-        <f>C50*D50</f>
+      <c r="A50" s="7"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="3">
+        <f>IF(D50="","",D50-E50)</f>
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="5"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="3">
-        <f>C51*D51</f>
+      <c r="A51" s="7"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="3">
+        <f>IF(D51="","",D51-E51)</f>
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="5"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="3">
-        <f>C52*D52</f>
+      <c r="A52" s="7"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="3">
+        <f>IF(D52="","",D52-E52)</f>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="5"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="3">
-        <f>C53*D53</f>
+      <c r="A53" s="7"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="3">
+        <f>IF(D53="","",D53-E53)</f>
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="5"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="3">
-        <f>C54*D54</f>
+      <c r="A54" s="7"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="3">
+        <f>IF(D54="","",D54-E54)</f>
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="5"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="3">
-        <f>C55*D55</f>
+      <c r="A55" s="7"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="3">
+        <f>IF(D55="","",D55-E55)</f>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="5"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="3">
-        <f>C56*D56</f>
+      <c r="A56" s="7"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="3">
+        <f>IF(D56="","",D56-E56)</f>
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="5"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="3">
-        <f>C57*D57</f>
+      <c r="A57" s="7"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="3">
+        <f>IF(D57="","",D57-E57)</f>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="5"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="3">
-        <f>C58*D58</f>
+      <c r="A58" s="7"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="3">
+        <f>IF(D58="","",D58-E58)</f>
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="5"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="3">
-        <f>C59*D59</f>
+      <c r="A59" s="7"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="3">
+        <f>IF(D59="","",D59-E59)</f>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="5"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="3">
-        <f>C60*D60</f>
+      <c r="A60" s="7"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="3">
+        <f>IF(D60="","",D60-E60)</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="3">
+        <f>IF(D61="","",D61-E61)</f>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="3">
+        <f>IF(D62="","",D62-E62)</f>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="3">
+        <f>IF(D63="","",D63-E63)</f>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="3">
+        <f>IF(D64="","",D64-E64)</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="3">
+        <f>IF(D65="","",D65-E65)</f>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="3">
+        <f>IF(D66="","",D66-E66)</f>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="3">
+        <f>IF(D67="","",D67-E67)</f>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="3">
+        <f>IF(D68="","",D68-E68)</f>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="3">
+        <f>IF(D69="","",D69-E69)</f>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="3">
+        <f>IF(D70="","",D70-E70)</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="3">
+        <f>IF(D71="","",D71-E71)</f>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="3">
+        <f>IF(D72="","",D72-E72)</f>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="3">
+        <f>IF(D73="","",D73-E73)</f>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="3">
+        <f>IF(D74="","",D74-E74)</f>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="3">
+        <f>IF(D75="","",D75-E75)</f>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="3">
+        <f>IF(D76="","",D76-E76)</f>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="3">
+        <f>IF(D77="","",D77-E77)</f>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="3">
+        <f>IF(D78="","",D78-E78)</f>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="3">
+        <f>IF(D79="","",D79-E79)</f>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="3">
+        <f>IF(D80="","",D80-E80)</f>
       </c>
     </row>
   </sheetData>
